--- a/tame_output/ON/bt/strategyON_20230726.xlsx
+++ b/tame_output/ON/bt/strategyON_20230726.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.7%</t>
+          <t>456.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2023-07-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.0%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1669"/>
+  <dimension ref="A1:G1670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39897,7 +39897,7 @@
         <v>45131</v>
       </c>
       <c r="B1669" t="n">
-        <v>2.874150344780631</v>
+        <v>2.87468608310342</v>
       </c>
       <c r="C1669" t="n">
         <v>3.004649846716132</v>
@@ -39913,6 +39913,29 @@
       </c>
       <c r="G1669" t="n">
         <v>4.279583967477222</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="2" t="n">
+        <v>45132</v>
+      </c>
+      <c r="B1670" t="n">
+        <v>2.878911290069859</v>
+      </c>
+      <c r="C1670" t="n">
+        <v>3.008212759175893</v>
+      </c>
+      <c r="D1670" t="n">
+        <v>1.519087873134845</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>3.615491484116084</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>2.124890201268481</v>
+      </c>
+      <c r="G1670" t="n">
+        <v>4.283146879936983</v>
       </c>
     </row>
   </sheetData>
